--- a/Письма от заказчика/Ведомость проверки результатов РД АСУ ТП (50164358 v1).xlsx
+++ b/Письма от заказчика/Ведомость проверки результатов РД АСУ ТП (50164358 v1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Projects\380-25_Ivanovo_TEC\Письма от заказчика\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29AAD89-45F4-4239-8290-243964C429AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86655308-4AFB-4D7B-9A45-5A2835C1BB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,13 +124,13 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <customWorkbookViews>
+    <customWorkbookView name="Неганов Евгений Валерьевич - Личное представление" guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" mergeInterval="0" personalView="1" maximized="1" xWindow="-11" yWindow="-11" windowWidth="2582" windowHeight="1402" activeSheetId="1"/>
+    <customWorkbookView name="Щелокова Ирина Геннадиевна - Личное представление" guid="{C7C38171-0C49-4819-A665-B56693D0589B}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="57" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
+    <customWorkbookView name="Алмакаева Анна Анатольевна - Личное представление" guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
+    <customWorkbookView name="Чернышев Иван Александрович - Личное представление" guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-16" yWindow="-16" windowWidth="3872" windowHeight="2092" activeSheetId="4"/>
+    <customWorkbookView name="Мустафаева Ксения Александровна - Личное представление" guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" mergeInterval="0" personalView="1" maximized="1" xWindow="9584" yWindow="-16" windowWidth="4832" windowHeight="2632" activeSheetId="5"/>
+    <customWorkbookView name="Брусничкин Александр Алексеевич - Личное представление" guid="{5393EB08-2805-4484-A848-F33FF939C496}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
     <customWorkbookView name="Батуева Дарья Александровна - Личное представление" guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Брусничкин Александр Алексеевич - Личное представление" guid="{5393EB08-2805-4484-A848-F33FF939C496}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Мустафаева Ксения Александровна - Личное представление" guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" mergeInterval="0" personalView="1" maximized="1" xWindow="9584" yWindow="-16" windowWidth="4832" windowHeight="2632" activeSheetId="5"/>
-    <customWorkbookView name="Чернышев Иван Александрович - Личное представление" guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" mergeInterval="0" personalView="1" maximized="1" xWindow="-16" yWindow="-16" windowWidth="3872" windowHeight="2092" activeSheetId="4"/>
-    <customWorkbookView name="Алмакаева Анна Анатольевна - Личное представление" guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" mergeInterval="0" personalView="1" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1936" windowHeight="1056" activeSheetId="1"/>
-    <customWorkbookView name="Щелокова Ирина Геннадиевна - Личное представление" guid="{C7C38171-0C49-4819-A665-B56693D0589B}" mergeInterval="0" personalView="1" maximized="1" xWindow="1912" yWindow="57" windowWidth="1296" windowHeight="1000" activeSheetId="1"/>
-    <customWorkbookView name="Неганов Евгений Валерьевич - Личное представление" guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" mergeInterval="0" personalView="1" maximized="1" xWindow="-11" yWindow="-11" windowWidth="2582" windowHeight="1402" activeSheetId="1"/>
   </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1284,6 +1284,27 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
@@ -1308,23 +1329,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1353,32 +1374,11 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2024,13 +2024,13 @@
       <c r="X1" s="3"/>
     </row>
     <row r="2" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -2052,13 +2052,13 @@
       <c r="X2" s="3"/>
     </row>
     <row r="3" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="100" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
       <c r="H3" s="30"/>
@@ -2080,12 +2080,12 @@
       <c r="X3" s="3"/>
     </row>
     <row r="4" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="100" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="97"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
       <c r="E4" s="48"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
@@ -2108,12 +2108,12 @@
       <c r="X4" s="3"/>
     </row>
     <row r="5" spans="1:256" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
       <c r="E5" s="48"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -2190,44 +2190,44 @@
       <c r="X7" s="3"/>
     </row>
     <row r="8" spans="1:256" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="98" t="s">
+      <c r="A8" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="93" t="s">
+      <c r="B8" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="93" t="s">
+      <c r="C8" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="93" t="s">
+      <c r="D8" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="93" t="s">
+      <c r="F8" s="92" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="93" t="s">
+      <c r="G8" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="93" t="s">
+      <c r="H8" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="96" t="s">
+      <c r="I8" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="93" t="s">
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="M8" s="93"/>
-      <c r="N8" s="96" t="s">
+      <c r="M8" s="92"/>
+      <c r="N8" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="O8" s="96"/>
-      <c r="P8" s="90" t="s">
+      <c r="O8" s="90"/>
+      <c r="P8" s="97" t="s">
         <v>46</v>
       </c>
       <c r="Q8" s="34" t="s">
@@ -2252,14 +2252,14 @@
       </c>
     </row>
     <row r="9" spans="1:256" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="98"/>
-      <c r="B9" s="93"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
+      <c r="A9" s="91"/>
+      <c r="B9" s="92"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="92"/>
       <c r="I9" s="25" t="s">
         <v>29</v>
       </c>
@@ -2281,7 +2281,7 @@
       <c r="O9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="P9" s="91"/>
+      <c r="P9" s="98"/>
       <c r="Q9" s="35"/>
       <c r="R9" s="35" t="s">
         <v>6</v>
@@ -2302,29 +2302,29 @@
       </c>
     </row>
     <row r="10" spans="1:256" x14ac:dyDescent="0.25">
-      <c r="A10" s="94" t="s">
+      <c r="A10" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="95" t="s">
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="88"/>
+      <c r="H10" s="88"/>
+      <c r="I10" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="94" t="s">
+      <c r="J10" s="89"/>
+      <c r="K10" s="89"/>
+      <c r="L10" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="M10" s="94"/>
-      <c r="N10" s="95" t="s">
+      <c r="M10" s="88"/>
+      <c r="N10" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="95"/>
+      <c r="O10" s="89"/>
       <c r="P10" s="47" t="s">
         <v>17</v>
       </c>
@@ -7029,7 +7029,7 @@
       <c r="I28" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="115" t="s">
+      <c r="J28" s="86" t="s">
         <v>132</v>
       </c>
       <c r="K28" s="43" t="s">
@@ -7303,7 +7303,7 @@
       <c r="I29" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J29" s="116"/>
+      <c r="J29" s="87"/>
       <c r="K29" s="43" t="s">
         <v>120</v>
       </c>
@@ -8945,7 +8945,7 @@
       <c r="I35" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J35" s="115" t="s">
+      <c r="J35" s="86" t="s">
         <v>128</v>
       </c>
       <c r="K35" s="43" t="s">
@@ -9219,7 +9219,7 @@
       <c r="I36" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="J36" s="116"/>
+      <c r="J36" s="87"/>
       <c r="K36" s="43" t="s">
         <v>120</v>
       </c>
@@ -9744,29 +9744,29 @@
       <c r="IV37" s="40"/>
     </row>
     <row r="38" spans="1:256" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="94" t="s">
+      <c r="A38" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="94"/>
-      <c r="C38" s="94"/>
-      <c r="D38" s="94"/>
-      <c r="E38" s="94"/>
-      <c r="F38" s="94"/>
-      <c r="G38" s="94"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="95" t="s">
+      <c r="B38" s="88"/>
+      <c r="C38" s="88"/>
+      <c r="D38" s="88"/>
+      <c r="E38" s="88"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="88"/>
+      <c r="H38" s="88"/>
+      <c r="I38" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="95"/>
-      <c r="K38" s="95"/>
-      <c r="L38" s="94" t="s">
+      <c r="J38" s="89"/>
+      <c r="K38" s="89"/>
+      <c r="L38" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="M38" s="94"/>
-      <c r="N38" s="95" t="s">
+      <c r="M38" s="88"/>
+      <c r="N38" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="O38" s="95"/>
+      <c r="O38" s="89"/>
       <c r="P38" s="47" t="s">
         <v>17</v>
       </c>
@@ -10035,7 +10035,7 @@
       <c r="I39" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J39" s="86" t="s">
+      <c r="J39" s="93" t="s">
         <v>121</v>
       </c>
       <c r="K39" s="43" t="s">
@@ -10311,7 +10311,7 @@
       <c r="I40" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J40" s="87"/>
+      <c r="J40" s="94"/>
       <c r="K40" s="43" t="s">
         <v>120</v>
       </c>
@@ -10585,7 +10585,7 @@
       <c r="I41" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="88"/>
+      <c r="J41" s="95"/>
       <c r="K41" s="43" t="s">
         <v>120</v>
       </c>
@@ -11980,10 +11980,10 @@
       <c r="J47" s="10"/>
       <c r="K47" s="11"/>
       <c r="L47" s="11"/>
-      <c r="M47" s="89" t="s">
+      <c r="M47" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="N47" s="89"/>
+      <c r="N47" s="96"/>
       <c r="O47" s="10"/>
       <c r="P47" s="11"/>
       <c r="Q47" s="11"/>
@@ -15126,23 +15126,45 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" scale="70" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A44">
-      <selection activeCell="C63" sqref="C63:D63"/>
+    <customSheetView guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A8">
+      <selection activeCell="F21" sqref="F21"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-      <autoFilter ref="B9:Y51" xr:uid="{1DF1433F-9ECE-4BBA-813A-67D353D873D1}"/>
+      <autoFilter ref="B9:Y31" xr:uid="{AF0A467E-5E9D-45C5-8171-B98059072B67}"/>
     </customSheetView>
-    <customSheetView guid="{5393EB08-2805-4484-A848-F33FF939C496}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A2">
-      <selection activeCell="K12" sqref="K12"/>
+    <customSheetView guid="{C7C38171-0C49-4819-A665-B56693D0589B}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C17">
+      <selection activeCell="K20" sqref="K20"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId2"/>
-      <autoFilter ref="B9:Y31" xr:uid="{F83DE9F3-49E1-4995-966E-412A61AAC0F3}"/>
+      <autoFilter ref="B9:Y31" xr:uid="{80BC905D-F58E-40DD-94E5-506F63B0B8B3}"/>
+    </customSheetView>
+    <customSheetView guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C11">
+      <selection activeCell="K23" sqref="K23"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId3"/>
+      <autoFilter ref="B9:Y31" xr:uid="{10BC3EE7-E4F8-417A-9FC5-51333150AD21}"/>
+    </customSheetView>
+    <customSheetView guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A233">
+      <selection activeCell="C238" sqref="C238:D238"/>
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId4"/>
+      <autoFilter ref="B10:Z230" xr:uid="{774686B4-84A5-4A00-85FD-D07F5384BDDB}">
+        <filterColumn colId="7">
+          <filters>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Производственое техническое управление_x000a_Отдел эксплуатации опасных производственных объектов"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_УПБОТиЭ_x000a_ОПБиПК"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление автоматизации производства"/>
+            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление производственно-технологической связи"/>
+            <filter val="ООО «НН Девелопмент»_x000a_Проектный офис реконструкции инфраструктурных объектов п. Тухард"/>
+          </filters>
+        </filterColumn>
+      </autoFilter>
     </customSheetView>
     <customSheetView guid="{603E59C3-0FC3-4A3F-B5D1-BCA0F806BD87}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" topLeftCell="K144">
       <selection activeCell="O76" sqref="O76"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="21" fitToHeight="0" orientation="landscape" r:id="rId3"/>
-      <autoFilter ref="B10:Z230" xr:uid="{6A38D106-4702-485A-92BC-F37979624B22}">
+      <pageSetup paperSize="9" scale="21" fitToHeight="0" orientation="landscape" r:id="rId5"/>
+      <autoFilter ref="B10:Z230" xr:uid="{430B1E67-2F28-427A-B3DD-97A39D8CAE80}">
         <filterColumn colId="7">
           <filters>
             <filter val="ИГН, ГТЭП"/>
@@ -15158,57 +15180,20 @@
         </filterColumn>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{26230550-FA05-4B27-A0C0-6D33BCFEA9B6}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" filter="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A233">
-      <selection activeCell="C238" sqref="C238:D238"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="landscape" r:id="rId4"/>
-      <autoFilter ref="B10:Z230" xr:uid="{0974C8C6-80A8-42BE-BE39-DD94D135D30A}">
-        <filterColumn colId="7">
-          <filters>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Производственое техническое управление_x000a_Отдел эксплуатации опасных производственных объектов"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_УПБОТиЭ_x000a_ОПБиПК"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление автоматизации производства"/>
-            <filter val="АО &quot;Норильсктрансгаз&quot;_x000a_Управление производственно-технологической связи"/>
-            <filter val="ООО «НН Девелопмент»_x000a_Проектный офис реконструкции инфраструктурных объектов п. Тухард"/>
-          </filters>
-        </filterColumn>
-      </autoFilter>
-    </customSheetView>
-    <customSheetView guid="{74164DD8-8A89-44C9-B878-FAEF59642254}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C11">
-      <selection activeCell="K23" sqref="K23"/>
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId5"/>
-      <autoFilter ref="B9:Y31" xr:uid="{86697836-398F-47E2-AE21-30295B6F383B}"/>
-    </customSheetView>
-    <customSheetView guid="{C7C38171-0C49-4819-A665-B56693D0589B}" scale="60" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="C17">
-      <selection activeCell="K20" sqref="K20"/>
+    <customSheetView guid="{5393EB08-2805-4484-A848-F33FF939C496}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A2">
+      <selection activeCell="K12" sqref="K12"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId6"/>
-      <autoFilter ref="B9:Y31" xr:uid="{0758D47F-A2C3-45F9-8290-C9382D8819B6}"/>
+      <autoFilter ref="B9:Y31" xr:uid="{E83C3695-596F-45E7-B6CA-6F56C2F13F22}"/>
     </customSheetView>
-    <customSheetView guid="{A875A593-D02B-4CD3-B0F4-C0344599AF32}" scale="55" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A8">
-      <selection activeCell="F21" sqref="F21"/>
+    <customSheetView guid="{DF12CA7C-123E-41ED-B931-BC6890EAA76F}" scale="70" showPageBreaks="1" fitToPage="1" printArea="1" showAutoFilter="1" hiddenRows="1" hiddenColumns="1" view="pageBreakPreview" topLeftCell="A44">
+      <selection activeCell="C63" sqref="C63:D63"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="24" fitToHeight="0" orientation="landscape" r:id="rId7"/>
-      <autoFilter ref="B9:Y31" xr:uid="{683400B9-EA62-41B1-8458-92FFACB91447}"/>
+      <autoFilter ref="B9:Y51" xr:uid="{915A182E-472F-48B7-A259-68505081C390}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="28">
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="J28:J29"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="J39:J41"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="P8:P9"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="L8:M8"/>
@@ -15217,11 +15202,26 @@
     <mergeCell ref="L38:M38"/>
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="N38:O38"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="I10:K10"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="J39:J41"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="N8:O8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="3">
@@ -15308,11 +15308,11 @@
       <c r="W1" s="3"/>
     </row>
     <row r="2" spans="1:255" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -15335,12 +15335,12 @@
       <c r="W2" s="3"/>
     </row>
     <row r="3" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+      <c r="A3" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="97"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
@@ -15362,11 +15362,11 @@
       <c r="W3" s="3"/>
     </row>
     <row r="4" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="s">
+      <c r="A4" s="100" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="97"/>
-      <c r="C4" s="97"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
       <c r="D4" s="48"/>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -15389,12 +15389,12 @@
       <c r="W4" s="3"/>
     </row>
     <row r="5" spans="1:255" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+      <c r="A5" s="100" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -15468,39 +15468,39 @@
       <c r="W7" s="3"/>
     </row>
     <row r="8" spans="1:255" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="113" t="s">
+      <c r="A8" s="115" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="93" t="s">
+      <c r="C8" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="93" t="s">
+      <c r="D8" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="93" t="s">
+      <c r="E8" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="93" t="s">
+      <c r="F8" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="105" t="s">
+      <c r="G8" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="106"/>
-      <c r="K8" s="93" t="s">
+      <c r="H8" s="114"/>
+      <c r="I8" s="114"/>
+      <c r="J8" s="113"/>
+      <c r="K8" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="93"/>
-      <c r="M8" s="96" t="s">
+      <c r="L8" s="92"/>
+      <c r="M8" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="N8" s="96"/>
-      <c r="O8" s="90" t="s">
+      <c r="N8" s="90"/>
+      <c r="O8" s="97" t="s">
         <v>30</v>
       </c>
       <c r="P8" s="34" t="s">
@@ -15525,22 +15525,22 @@
       </c>
     </row>
     <row r="9" spans="1:255" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="114"/>
-      <c r="B9" s="104"/>
-      <c r="C9" s="93"/>
-      <c r="D9" s="93"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="93"/>
+      <c r="A9" s="116"/>
+      <c r="B9" s="111"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="92"/>
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
       <c r="G9" s="25" t="s">
         <v>29</v>
       </c>
       <c r="H9" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="105" t="s">
+      <c r="I9" s="112" t="s">
         <v>3</v>
       </c>
-      <c r="J9" s="106"/>
+      <c r="J9" s="113"/>
       <c r="K9" s="19" t="s">
         <v>8</v>
       </c>
@@ -15553,7 +15553,7 @@
       <c r="N9" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="O9" s="91"/>
+      <c r="O9" s="98"/>
       <c r="P9" s="35"/>
       <c r="Q9" s="35" t="s">
         <v>6</v>
@@ -15574,28 +15574,28 @@
       </c>
     </row>
     <row r="10" spans="1:255" x14ac:dyDescent="0.25">
-      <c r="A10" s="94" t="s">
+      <c r="A10" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="94"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="110" t="s">
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="88"/>
+      <c r="G10" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="94" t="s">
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="103"/>
+      <c r="K10" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="94"/>
-      <c r="M10" s="95" t="s">
+      <c r="L10" s="88"/>
+      <c r="M10" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="N10" s="95"/>
+      <c r="N10" s="89"/>
       <c r="O10" s="47" t="s">
         <v>17</v>
       </c>
@@ -15619,8 +15619,8 @@
       <c r="F11" s="59"/>
       <c r="G11" s="70"/>
       <c r="H11" s="70"/>
-      <c r="I11" s="108"/>
-      <c r="J11" s="109"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="105"/>
       <c r="K11" s="6"/>
       <c r="L11" s="16"/>
       <c r="M11" s="71"/>
@@ -15878,8 +15878,8 @@
       <c r="F12" s="59"/>
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
-      <c r="I12" s="108"/>
-      <c r="J12" s="109"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="105"/>
       <c r="K12" s="6"/>
       <c r="L12" s="16"/>
       <c r="M12" s="71"/>
@@ -16137,8 +16137,8 @@
       <c r="F13" s="59"/>
       <c r="G13" s="70"/>
       <c r="H13" s="70"/>
-      <c r="I13" s="108"/>
-      <c r="J13" s="109"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="105"/>
       <c r="K13" s="6"/>
       <c r="L13" s="16"/>
       <c r="M13" s="71"/>
@@ -16396,8 +16396,8 @@
       <c r="F14" s="59"/>
       <c r="G14" s="70"/>
       <c r="H14" s="70"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="109"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="105"/>
       <c r="K14" s="6"/>
       <c r="L14" s="16"/>
       <c r="M14" s="71"/>
@@ -16655,8 +16655,8 @@
       <c r="F15" s="59"/>
       <c r="G15" s="70"/>
       <c r="H15" s="70"/>
-      <c r="I15" s="108"/>
-      <c r="J15" s="109"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="105"/>
       <c r="K15" s="6"/>
       <c r="L15" s="16"/>
       <c r="M15" s="71"/>
@@ -16904,28 +16904,28 @@
       <c r="IU15" s="40"/>
     </row>
     <row r="16" spans="1:255" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="100" t="s">
+      <c r="A16" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="110" t="s">
+      <c r="B16" s="108"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="112"/>
-      <c r="K16" s="94" t="s">
+      <c r="H16" s="102"/>
+      <c r="I16" s="102"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="L16" s="94"/>
-      <c r="M16" s="95" t="s">
+      <c r="L16" s="88"/>
+      <c r="M16" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="95"/>
+      <c r="N16" s="89"/>
       <c r="O16" s="47" t="s">
         <v>17</v>
       </c>
@@ -17183,8 +17183,8 @@
       <c r="F17" s="59"/>
       <c r="G17" s="70"/>
       <c r="H17" s="70"/>
-      <c r="I17" s="108"/>
-      <c r="J17" s="109"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="105"/>
       <c r="K17" s="6"/>
       <c r="L17" s="16"/>
       <c r="M17" s="71"/>
@@ -17442,8 +17442,8 @@
       <c r="F18" s="59"/>
       <c r="G18" s="70"/>
       <c r="H18" s="70"/>
-      <c r="I18" s="108"/>
-      <c r="J18" s="109"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="105"/>
       <c r="K18" s="6"/>
       <c r="L18" s="16"/>
       <c r="M18" s="71"/>
@@ -17952,18 +17952,18 @@
         <v>28</v>
       </c>
       <c r="B20" s="63"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="99"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
       <c r="E20" s="7"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="10"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
-      <c r="K20" s="89" t="s">
+      <c r="K20" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="L20" s="89"/>
+      <c r="L20" s="96"/>
       <c r="M20" s="23"/>
       <c r="N20" s="10"/>
       <c r="O20" s="11"/>
@@ -18221,8 +18221,8 @@
       <c r="H21" s="10"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
-      <c r="K21" s="89"/>
-      <c r="L21" s="89"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="96"/>
       <c r="M21" s="23"/>
       <c r="N21" s="10"/>
       <c r="O21" s="11"/>
@@ -20579,23 +20579,6 @@
   </sheetData>
   <autoFilter ref="K1:K33" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="33">
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:C4"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B8:B9"/>
@@ -20612,6 +20595,23 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="I18:J18"/>
     <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M8:N8"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:K15">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
